--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261030.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261030.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -790,7 +790,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17723,7 +17723,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19733,7 +19733,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19867,7 +19867,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22815,7 +22815,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S342" s="1" t="n">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S343" s="1" t="n">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S344" s="1" t="n">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S345" s="1" t="n">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S346" s="1" t="n">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S347" s="1" t="n">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S348" s="1" t="n">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S349" s="1" t="n">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S350" s="1" t="n">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S351" s="1" t="n">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S352" s="1" t="n">
@@ -24222,7 +24222,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S353" s="1" t="n">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S354" s="1" t="n">
@@ -24356,7 +24356,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S355" s="1" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S356" s="1" t="n">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S357" s="1" t="n">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S358" s="1" t="n">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S359" t="inlineStr"/>
@@ -24657,7 +24657,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S360" t="inlineStr"/>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S361" t="inlineStr"/>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="S362" t="inlineStr"/>
